--- a/output/2026-09-08_23_Croazia_Sisacko-moslavacka_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-08_23_Croazia_Sisacko-moslavacka_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ingrosso/dettaglio cuscinetti, cinghie trapezoidali, catene, guarnizioni, o-ring, prodotti Loctite, oli e lubrificanti, minuteria metallica, dischi da taglio/smerigliatura (KEDAS). Indirizzo: Nikole Šipuša 17, 44000 Sisak. Verificato tramite ricerca web (fininfo.hr, companywall.hr, roto-sisak.hr).</t>
+          <t>Ingrosso/dettaglio cuscinetti, cinghie trapezoidali, catene, guarnizioni, o-ring, prodotti Loctite, oli e lubrificanti, minuteria metallica, dischi da taglio/smerigliatura (KEDAS). Indirizzo: Nikole Šipuša 17, 44000 Sisak. Verificato tramite ricerca web (fininfo.hr, companywall.hr, roto-sisak.hr). [DUPLICATO — vedi anche: 2026-09-08_21_Croazia_Sisacko-moslavacka_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -615,7 +615,6 @@
           <t>044 813 884</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Idraulica, pneumatica, automazione, diagnostica e assistenza tecnica industriale. Indirizzo: Božičevićeva 14, 44250 Petrinja. Email non reperita/pubblicata: campo lasciato vuoto. Verificato tramite ricerca web (hibos.hr, tvrtke.hr).</t>
@@ -633,7 +632,6 @@
           <t>ANDE d.o.o.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Sisačko-moslavačka</t>
@@ -649,7 +647,6 @@
           <t>044 545 006</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Servizi/fornitura idraulica-pneumatica. Indirizzo: Mije Goričkog 44, 44000 Sisak. Nessun sito web reperito: campo lasciato vuoto. Verificato tramite ricerca web (tvrtke.hr, radno-vrijeme.com).</t>

--- a/output/2026-09-08_23_Croazia_Sisacko-moslavacka_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-08_23_Croazia_Sisacko-moslavacka_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
